--- a/Neo_Phoenix/reports/daily_check.xlsx
+++ b/Neo_Phoenix/reports/daily_check.xlsx
@@ -8,11 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="DaySummary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Game1_01_海保大－広島大" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game1_01_川医大－岡大医" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game2_02_島根大－吉備国" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Game3_03_海保大－広島大" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'DaySummary'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_海保大－広島大'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_川医大－岡大医'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Game2_02_島根大－吉備国'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Game3_03_海保大－広島大'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -544,7 +548,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-14 10:39:22</t>
+          <t>2026-09-14 13:41:45</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -588,7 +592,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>1試合</t>
+          <t>3試合</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -598,7 +602,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>14件</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -663,12 +667,12 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>□ 01_海保大－広島大</t>
+          <t>□ 01_川医大－岡大医</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2回表 1点目　非自責</t>
+          <t>1回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -687,17 +691,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>□ 01_海保大－広島大</t>
+          <t>□ 01_川医大－岡大医</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>5回表 1点目　非自責</t>
+          <t>2回表 1点目　非自責</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Virtual3アウト</t>
+          <t>失策生還</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -711,12 +715,12 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>□ 01_海保大－広島大</t>
+          <t>□ 01_川医大－岡大医</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>6回表 1点目　非自責</t>
+          <t>2回表 2点目　非自責</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -735,17 +739,17 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>□ 01_海保大－広島大</t>
+          <t>□ 01_川医大－岡大医</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>7回裏 1点目　非自責</t>
+          <t>4回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -755,6 +759,246 @@
       </c>
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>7回表 3点目　非自責</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>9回表 6点目　非自責</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>9回表 7点目　非自責</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>9回表 8点目　非自責</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>失策出塁</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>9回裏 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>9回裏 2点目　非自責</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_海保大－広島大</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2回表 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_海保大－広島大</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>5回表 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_海保大－広島大</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>6回表 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_海保大－広島大</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>7回裏 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -767,6 +1011,2124 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EasyScoreJudge Phoenix Daily Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>01_川医大－岡大医：EasyScore補正票</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>試合名</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>01_川医大－岡大医</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>確認状態</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>□未確認  □補正済  □再確認</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>総得点</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>自責候補</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>本日の補正</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>補正作業</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>走者/内容</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 大</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>横山 大輔</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2回表 2点目</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>三好 嶺和</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr"/>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr"/>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>竹内 宏仁</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>鞍留 駿斗</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr"/>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 大</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>横山 大輔</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2回表 2点目</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>2回表 2点目</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>佐藤 大</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>竹内 宏仁</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>横山 大輔</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>三好 嶺和</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>寺西 航太朗</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 3点目</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 3点目</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>平井 佑希</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 4点目</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>4回裏 4点目</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>大谷 駿羽</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>平井 貴之</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>野島 蒼也</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>鞍留 駿斗</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>松本 武大</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>鞍留 駿斗</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>山谷 柊斗</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 3点目</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 3点目</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>鞍留 駿斗</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>三好 嶺和</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="1" t="inlineStr"/>
+      <c r="B39" s="1" t="inlineStr"/>
+      <c r="C39" s="1" t="inlineStr"/>
+      <c r="D39" s="1" t="inlineStr"/>
+      <c r="E39" s="1" t="inlineStr"/>
+      <c r="F39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="1" t="inlineStr"/>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr"/>
+      <c r="D41" s="1" t="inlineStr"/>
+      <c r="E41" s="1" t="inlineStr"/>
+      <c r="F41" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EasyScoreJudge Phoenix Daily Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>02_島根大－吉備国：EasyScore補正票</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>試合名</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>02_島根大－吉備国</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>確認状態</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>□未確認  □補正済  □再確認</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>総得点</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>自責候補</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>本日の補正</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>補正作業</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>走者/内容</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>7回表 3点目</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>石原 大暉</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>9回表 6点目</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>今井 悠生</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>9回表 7点目</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>横地 翔来</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>9回表 8点目</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>失策出塁</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>森脇 純大</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>手銭 颯太</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>住川 晴弥人</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr"/>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>竹谷 友輝</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>苅野 幸元</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr"/>
+      <c r="D26" s="1" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>竹谷 友輝</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>日笠 裕太</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>2回表 1点目</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>服部 貫太</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>服部 貫太</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>7回表 1点目</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>7回表 1点目</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>岸渕 一真</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>7回表 2点目</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>7回表 2点目</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>増井 颯</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>7回表 3点目</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>7回表 3点目</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>石原 大暉</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>9回表 1点目</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>9回表 1点目</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>石原 大暉</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>9回表 2点目</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>9回表 2点目</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>服部 貫太</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>9回表 3点目</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>9回表 3点目</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>小村 瞬平</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>9回表 4点目</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>9回表 4点目</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>古野 正裕</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>9回表 5点目</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>9回表 5点目</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>宮脇 大和</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>野坂 宗汰</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>9回表 6点目</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>9回表 6点目</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>今井 悠生</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>9回表 7点目</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>9回表 7点目</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>失策生還</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>横地 翔来</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>9回表 8点目</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>9回表 8点目</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>失策出塁</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>森脇 純大</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>手銭 颯太</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>9回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>住川 晴弥人</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="1" t="inlineStr"/>
+      <c r="B44" s="1" t="inlineStr"/>
+      <c r="C44" s="1" t="inlineStr"/>
+      <c r="D44" s="1" t="inlineStr"/>
+      <c r="E44" s="1" t="inlineStr"/>
+      <c r="F44" s="1" t="inlineStr"/>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="1" t="inlineStr"/>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr"/>
+      <c r="D46" s="1" t="inlineStr"/>
+      <c r="E46" s="1" t="inlineStr"/>
+      <c r="F46" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -798,7 +3160,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>01_海保大－広島大：EasyScore補正票</t>
+          <t>03_海保大－広島大：EasyScore補正票</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -823,7 +3185,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>01_海保大－広島大</t>
+          <t>03_海保大－広島大</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>

--- a/Neo_Phoenix/reports/daily_check.xlsx
+++ b/Neo_Phoenix/reports/daily_check.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="DaySummary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Game1_01_山口大－鳥大医" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game1_01_広大医－広修大" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'DaySummary'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_山口大－鳥大医'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_広大医－広修大'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18 17:08:24</t>
+          <t>2026-09-23 15:55:17</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -663,17 +663,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>□ 01_山口大－鳥大医</t>
+          <t>□ 01_広大医－広修大</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>6回裏 1点目　非自責</t>
+          <t>2回裏 5点目　非自責</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>失策出塁</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -687,17 +687,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>□ 01_山口大－鳥大医</t>
+          <t>□ 01_広大医－広修大</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>6回裏 2点目　非自責</t>
+          <t>6回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -711,12 +711,12 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>□ 01_山口大－鳥大医</t>
+          <t>□ 01_広大医－広修大</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>8回表 1点目　非自責</t>
+          <t>6回裏 2点目　非自責</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -731,30 +731,6 @@
       </c>
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>□ 01_山口大－鳥大医</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>9回裏 1点目　非自責</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Virtual3アウト</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr"/>
-      <c r="F13" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -772,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -798,7 +774,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>01_山口大－鳥大医：EasyScore補正票</t>
+          <t>01_広大医－広修大：EasyScore補正票</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -823,7 +799,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>01_山口大－鳥大医</t>
+          <t>01_広大医－広修大</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -854,7 +830,7 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -862,7 +838,7 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -941,7 +917,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>6回裏 1点目</t>
+          <t>2回裏 5点目</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -951,12 +927,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>失策出塁</t>
+          <t>Virtual生還不能</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>魚崎 健太</t>
+          <t>伊部 将大</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -973,7 +949,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6回裏 2点目</t>
+          <t>6回裏 1点目</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -983,12 +959,12 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>失策生還</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>土居 映斗</t>
+          <t>伊部 将大</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
@@ -1005,7 +981,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>8回表 1点目</t>
+          <t>6回裏 2点目</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1020,7 +996,7 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>川野 凌舞</t>
+          <t>久保 旺介</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
@@ -1030,78 +1006,60 @@
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>9回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Virtual3アウト</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>北垣 安哉人</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="inlineStr"/>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr"/>
+      <c r="D12" s="1" t="inlineStr"/>
+      <c r="E12" s="1" t="inlineStr"/>
+      <c r="F12" s="1" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="1" t="inlineStr"/>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr"/>
-      <c r="D13" s="1" t="inlineStr"/>
-      <c r="E13" s="1" t="inlineStr"/>
-      <c r="F13" s="1" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>投手サマリー</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>鬼頭 陸歩</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>上田 陽己</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>失点</t>
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="C15" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="1" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr"/>
@@ -1109,9 +1067,9 @@
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="C16" s="1" t="n">
@@ -1122,32 +1080,32 @@
       <c r="F16" s="1" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="1" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>今村 一翔</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
         </is>
       </c>
       <c r="C17" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="1" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>北垣 安哉人</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>失点</t>
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
         </is>
       </c>
       <c r="C18" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1" t="inlineStr"/>
       <c r="E18" s="1" t="inlineStr"/>
@@ -1155,13 +1113,13 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="1" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D19" s="1" t="inlineStr"/>
       <c r="E19" s="1" t="inlineStr"/>
@@ -1169,174 +1127,292 @@
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr"/>
       <c r="D20" s="1" t="inlineStr"/>
       <c r="E20" s="1" t="inlineStr"/>
       <c r="F20" s="1" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>濱﨑 和葉</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>失点</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>自責</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>鬼頭 陸歩</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>手島 悠</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>鬼頭 陸歩</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>後田 悠翔</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>末冨 翼</t>
+          <t>2回裏 3点目</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>失点</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
+          <t>2回裏 3点目</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>鬼頭 陸歩</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>齋藤 航大</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 4点目</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 4点目</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>自責</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>鬼頭 陸歩</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>西村 侑哉</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 5点目</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 5点目</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>非自責</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>伊部 将大</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>5回表 1点目</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>5回表 1点目</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>今村 一翔</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>坂尾 太智</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>得点詳細</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>理由</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>走者</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>確認</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>5回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>鬼頭 陸歩</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>手島 悠</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>3回表 1点目</t>
+          <t>6回裏 1点目</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3回表 1点目</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>6回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>上田 陽己</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>吉尾 蒼太</t>
+          <t>伊部 将大</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -1348,27 +1424,27 @@
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>5回表 1点目</t>
+          <t>6回裏 2点目</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>5回表 1点目</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
+          <t>6回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>上田 陽己</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>西口 世那</t>
+          <t>久保 旺介</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -1378,280 +1454,56 @@
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>5回表 2点目</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>5回表 2点目</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>上田 陽己</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>亀田 柊悟</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
+      <c r="A31" s="1" t="inlineStr"/>
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr"/>
+      <c r="D31" s="1" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr"/>
+      <c r="F31" s="1" t="inlineStr"/>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>6回表 1点目</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>6回表 1点目</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>北垣 安哉人</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>川野 凌舞</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>6回裏 1点目</t>
-        </is>
-      </c>
+      <c r="A33" s="1" t="inlineStr"/>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>6回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>失策出塁</t>
-        </is>
-      </c>
-      <c r="E33" s="1" t="inlineStr">
-        <is>
-          <t>魚崎 健太</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>6回裏 2点目</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>6回裏 2点目</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>失策生還</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>土居 映斗</t>
-        </is>
-      </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>7回表 1点目</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>7回表 1点目</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>自責</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>北垣 安哉人</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>亀田 柊悟</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>8回表 1点目</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>8回表 1点目</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>Virtual3アウト</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>川野 凌舞</t>
-        </is>
-      </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>9回裏 1点目</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>9回裏 1点目</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>非自責</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>Virtual3アウト</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>北垣 安哉人</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Review詳細</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>レベル</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>信頼度</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr"/>
+      <c r="D33" s="1" t="inlineStr"/>
+      <c r="E33" s="1" t="inlineStr"/>
+      <c r="F33" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Neo_Phoenix/reports/daily_check.xlsx
+++ b/Neo_Phoenix/reports/daily_check.xlsx
@@ -8,11 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="DaySummary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Game1_01_広大医－広修大" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game1_01_下市大－山口大" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Game2_02_鳥大医－岡山大" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Game3_03_広大医－広修大" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'DaySummary'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_広大医－広修大'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Game1_01_下市大－山口大'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Game2_02_鳥大医－岡山大'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Game3_03_広大医－広修大'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -544,7 +548,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23 15:55:17</t>
+          <t>2026-09-28 14:33:23</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
@@ -588,7 +592,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>1試合</t>
+          <t>3試合</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -598,7 +602,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>15件</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -663,17 +667,17 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>□ 01_広大医－広修大</t>
+          <t>□ 01_下市大－山口大</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2回裏 5点目　非自責</t>
+          <t>1回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Virtual生還不能</t>
+          <t>Virtual3アウト</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -687,17 +691,17 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>□ 01_広大医－広修大</t>
+          <t>□ 01_下市大－山口大</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>6回裏 1点目　非自責</t>
+          <t>7回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Virtual3アウト</t>
+          <t>失策出塁</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -711,17 +715,17 @@
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>□ 01_広大医－広修大</t>
+          <t>□ 02_鳥大医－岡山大</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>6回裏 2点目　非自責</t>
+          <t>1回裏 1点目　非自責</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Virtual3アウト</t>
+          <t>捕逸生還</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -731,6 +735,294 @@
       </c>
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 2点目　非自責</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 3点目　非自責</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 4点目　非自責</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 5点目　非自責</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 6点目　非自責</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 7点目　非自責</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 8点目　非自責</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>4回表 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>□ 02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>4回表 2点目　非自責</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_広大医－広修大</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2回裏 5点目　非自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Virtual生還不能</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_広大医－広修大</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>6回裏 1点目　非自責</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>□ 03_広大医－広修大</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>6回裏 2点目　非自責</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -743,6 +1035,1886 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EasyScoreJudge Phoenix Daily Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>01_下市大－山口大：EasyScore補正票</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>試合名</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>01_下市大－山口大</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>確認状態</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>□未確認  □補正済  □再確認</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>総得点</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>自責候補</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>本日の補正</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>補正作業</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>走者/内容</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>亀田 柊悟 振逃無死一塁</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>失策出塁</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>松村 伊恭</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="inlineStr"/>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr"/>
+      <c r="D11" s="1" t="inlineStr"/>
+      <c r="E11" s="1" t="inlineStr"/>
+      <c r="F11" s="1" t="inlineStr"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>安河内 颯人</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>濱﨑 和葉</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr"/>
+      <c r="E17" s="1" t="inlineStr"/>
+      <c r="F17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>亀田 柊悟 振逃無死一塁</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>6回表 1点目</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>6回表 1点目</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>濱﨑 和葉</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>藤濤 英介</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>6回表 2点目</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>6回表 2点目</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>濱﨑 和葉</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>井上 翼</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>6回表 3点目</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>6回表 3点目</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>濱﨑 和葉</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>小原 章裕</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>失策出塁</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>松村 伊恭</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>8回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>8回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>安河内 颯人</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>竹中 優作</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr"/>
+      <c r="D27" s="1" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
+      <c r="F27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="1" t="inlineStr"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr"/>
+      <c r="D29" s="1" t="inlineStr"/>
+      <c r="E29" s="1" t="inlineStr"/>
+      <c r="F29" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EasyScoreJudge Phoenix Daily Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>02_鳥大医－岡山大：EasyScore補正票</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>試合名</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>02_鳥大医－岡山大</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>確認状態</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>□未確認  □補正済  □再確認</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>総得点</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>自責候補</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>本日の補正</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>補正作業</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>走者/内容</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>作業</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>捕逸生還</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>石田 晋太朗</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>上原 大河</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 3点目</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>古川 夢翔</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 4点目</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>石田 晋太朗</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 5点目</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>山口 拓真</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 6点目</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>小林 拓真</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 7点目</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>前田 光晴</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 8点目</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>橋口 怜</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>魚崎 健太</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>4回表 2点目</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>小野 唯斗</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>投手サマリー</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>山端 結陽</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>中曽根 熙也</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>黒木 紳之介</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>失点</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="1" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
+      <c r="F27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="1" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1" t="inlineStr"/>
+      <c r="E29" s="1" t="inlineStr"/>
+      <c r="F29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="1" t="inlineStr"/>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr"/>
+      <c r="D30" s="1" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr"/>
+      <c r="F30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>得点詳細</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>走者</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>1回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>捕逸生還</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>石田 晋太朗</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>山端 結陽</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>杉原 誇馬</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 2点目</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 2点目</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>上原 大河</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 3点目</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 3点目</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>古川 夢翔</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 4点目</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 4点目</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>石田 晋太朗</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 5点目</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 5点目</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>山口 拓真</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 6点目</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 6点目</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>小林 拓真</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 7点目</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 7点目</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>前田 光晴</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 8点目</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>2回裏 8点目</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>橋口 怜</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>3回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>山端 結陽</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>古川 夢翔</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>4回表 1点目</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>魚崎 健太</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>4回表 2点目</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>4回表 2点目</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>非自責</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Virtual3アウト</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>小野 唯斗</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>7回表 1点目</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>7回表 1点目</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>黒木 紳之介</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>漆畑 拓斗</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>7回表 2点目</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>7回表 2点目</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>黒木 紳之介</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>三好 海都</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>7回裏 1点目</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>自責</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>山端 結陽</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>小林 拓真</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="1" t="inlineStr"/>
+      <c r="B47" s="1" t="inlineStr"/>
+      <c r="C47" s="1" t="inlineStr"/>
+      <c r="D47" s="1" t="inlineStr"/>
+      <c r="E47" s="1" t="inlineStr"/>
+      <c r="F47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Review詳細</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>レベル</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>信頼度</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr"/>
+      <c r="D49" s="1" t="inlineStr"/>
+      <c r="E49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -774,7 +2946,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>01_広大医－広修大：EasyScore補正票</t>
+          <t>03_広大医－広修大：EasyScore補正票</t>
         </is>
       </c>
       <c r="B2" s="1" t="n"/>
@@ -799,7 +2971,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>01_広大医－広修大</t>
+          <t>03_広大医－広修大</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
